--- a/Hand_edited_log/1/student/AnhDThe187386/TC6/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/AnhDThe187386/TC6/GradeDetail.xlsx
@@ -158,10 +158,7 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIL</x:t>
+    <x:t>PASS</x:t>
   </x:si>
   <x:si>
     <x:t>SYN, ACK</x:t>
@@ -182,10 +179,25 @@
     <x:t>Data transfer in progress</x:t>
   </x:si>
   <x:si>
+    <x:t>Sabc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"StudentId":"Sabc","Name":null,"Major":null,"Year":null,"GPA":null,"Status":"error","Message":"Student not found"}</x:t>
+  </x:si>
+  <x:si>
     <x:t>FIN, ACK</x:t>
   </x:si>
   <x:si>
     <x:t>Closing connection (FIN-ACK)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PARTIAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S111</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"StudentId":"S111","Name":null,"Major":null,"Year":null,"GPA":null,"Status":"error","Message":"Student not found"}</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -212,7 +224,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -221,7 +233,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFB6C1"/>
+        <x:fgColor rgb="FF90EE90"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFF00"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -244,7 +261,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="3">
+  <x:cellStyleXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -254,8 +271,11 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="3">
+  <x:cellXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -265,6 +285,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -937,11 +961,11 @@
     <x:col min="8" max="8" width="4.996339" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="10.853482" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="29.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
-    <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
+    <x:col min="15" max="15" width="108.853482" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="14.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -1027,22 +1051,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="L2" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="M2" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N2" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P2" s="2" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="L2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P2" s="2" t="s">
-        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:16">
@@ -1062,11 +1086,11 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -1077,22 +1101,22 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="M3" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N3" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P3" s="2" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="L3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P3" s="2" t="s">
-        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16">
@@ -1112,11 +1136,11 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -1127,22 +1151,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="L4" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="M4" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N4" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P4" s="2" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="L4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P4" s="2" t="s">
-        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:16">
@@ -1162,37 +1186,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G5" s="0" t="s">
+      <x:c r="H5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="L5" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="M5" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N5" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O5" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I5" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="K5" s="0" t="s">
+      <x:c r="P5" s="2" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="L5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P5" s="2" t="s">
-        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:16">
@@ -1212,11 +1236,11 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -1227,22 +1251,22 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="L6" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="M6" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N6" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P6" s="2" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="L6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P6" s="2" t="s">
-        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:16">
@@ -1262,11 +1286,11 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -1277,22 +1301,22 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="L7" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="M7" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N7" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O7" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="P7" s="2" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="L7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P7" s="2" t="s">
-        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:16">
@@ -1312,11 +1336,11 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -1327,22 +1351,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="L8" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="M8" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N8" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P8" s="2" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="L8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P8" s="2" t="s">
-        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:16">
@@ -1362,37 +1386,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K9" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="K9" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="N9" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="O9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P9" s="2" t="s">
-        <x:v>47</x:v>
+      <x:c r="P9" s="3" t="s">
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:16">
@@ -1412,11 +1436,11 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G10" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="H10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -1427,22 +1451,22 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="N10" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="O10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P10" s="2" t="s">
-        <x:v>47</x:v>
+      <x:c r="P10" s="3" t="s">
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:16">
@@ -1462,37 +1486,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="K11" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="H11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I11" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="J11" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="K11" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="L11" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M11" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="N11" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="O11" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P11" s="2" t="s">
-        <x:v>47</x:v>
+      <x:c r="P11" s="3" t="s">
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:16">
@@ -1512,11 +1536,11 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G12" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="H12" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -1527,22 +1551,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="L12" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M12" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="N12" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="O12" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P12" s="2" t="s">
-        <x:v>47</x:v>
+      <x:c r="P12" s="3" t="s">
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:16">
@@ -1577,22 +1601,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="L13" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="M13" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N13" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P13" s="2" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="L13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P13" s="2" t="s">
-        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:16">
@@ -1612,11 +1636,11 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="G14" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="H14" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -1627,22 +1651,22 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="L14" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="M14" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N14" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P14" s="2" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="L14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P14" s="2" t="s">
-        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:16">
@@ -1662,11 +1686,11 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G15" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G15" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="H15" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -1677,22 +1701,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="L15" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="M15" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N15" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P15" s="2" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="L15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P15" s="2" t="s">
-        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:16">
@@ -1712,11 +1736,11 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G16" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G16" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="H16" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -1727,22 +1751,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="L16" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="M16" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N16" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O16" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="P16" s="2" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="L16" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M16" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N16" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O16" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P16" s="2" t="s">
-        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -1762,11 +1786,11 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G17" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G17" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="H17" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -1777,22 +1801,22 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="L17" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="M17" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N17" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P17" s="2" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="L17" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M17" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N17" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O17" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P17" s="2" t="s">
-        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -1812,11 +1836,11 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G18" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G18" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="H18" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -1827,22 +1851,22 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="L18" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="M18" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N18" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O18" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="P18" s="2" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="L18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P18" s="2" t="s">
-        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:16">
@@ -1862,11 +1886,11 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G19" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G19" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="H19" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -1877,22 +1901,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="L19" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="M19" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N19" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P19" s="2" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="L19" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M19" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N19" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O19" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P19" s="2" t="s">
-        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:16">
@@ -1912,37 +1936,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H20" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I20" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="J20" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K20" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="H20" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I20" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="J20" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="K20" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="L20" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M20" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="N20" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="O20" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P20" s="2" t="s">
-        <x:v>47</x:v>
+      <x:c r="P20" s="3" t="s">
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:16">
@@ -1962,11 +1986,11 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G21" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G21" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="H21" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -1977,22 +2001,22 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="L21" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M21" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="N21" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="O21" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P21" s="2" t="s">
-        <x:v>47</x:v>
+      <x:c r="P21" s="3" t="s">
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2012,37 +2036,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H22" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I22" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="J22" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="K22" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="H22" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I22" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="J22" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="K22" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="L22" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M22" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="N22" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="O22" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P22" s="2" t="s">
-        <x:v>47</x:v>
+      <x:c r="P22" s="3" t="s">
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:16">
@@ -2062,11 +2086,11 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G23" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G23" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="H23" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -2077,22 +2101,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="L23" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M23" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="N23" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="O23" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P23" s="2" t="s">
-        <x:v>47</x:v>
+      <x:c r="P23" s="3" t="s">
+        <x:v>57</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Hand_edited_log/1/student/AnhDThe187386/TC6/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/AnhDThe187386/TC6/GradeDetail.xlsx
@@ -140,6 +140,12 @@
     <x:t>ActualData</x:t>
   </x:si>
   <x:si>
+    <x:t>ActualSourcePort</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ActualDestPort</x:t>
+  </x:si>
+  <x:si>
     <x:t>NetworkResult</x:t>
   </x:si>
   <x:si>
@@ -173,15 +179,24 @@
     <x:t>Connection established</x:t>
   </x:si>
   <x:si>
+    <x:t>Connection acknowledged (ACK)</x:t>
+  </x:si>
+  <x:si>
     <x:t>PSH, ACK</x:t>
   </x:si>
   <x:si>
     <x:t>Data transfer in progress</x:t>
   </x:si>
   <x:si>
+    <x:t>Client sending data</x:t>
+  </x:si>
+  <x:si>
     <x:t>Sabc</x:t>
   </x:si>
   <x:si>
+    <x:t>Server sending data</x:t>
+  </x:si>
+  <x:si>
     <x:t>{"StudentId":"Sabc","Name":null,"Major":null,"Year":null,"GPA":null,"Status":"error","Message":"Student not found"}</x:t>
   </x:si>
   <x:si>
@@ -191,7 +206,13 @@
     <x:t>Closing connection (FIN-ACK)</x:t>
   </x:si>
   <x:si>
+    <x:t>Server closing connection</x:t>
+  </x:si>
+  <x:si>
     <x:t>PARTIAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Client closing connection</x:t>
   </x:si>
   <x:si>
     <x:t>S111</x:t>
@@ -948,7 +969,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P23"/>
+  <x:dimension ref="A1:R23"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
@@ -966,10 +987,12 @@
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="108.853482" style="0" customWidth="1"/>
-    <x:col min="16" max="16" width="14.139196" style="0" customWidth="1"/>
+    <x:col min="16" max="16" width="16.424911" style="0" customWidth="1"/>
+    <x:col min="17" max="17" width="14.424911" style="0" customWidth="1"/>
+    <x:col min="18" max="18" width="14.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:16" s="1" customFormat="1">
+    <x:row r="1" spans="1:18" s="1" customFormat="1">
       <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -1018,8 +1041,14 @@
       <x:c r="P1" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:16">
+      <x:c r="Q1" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="R1" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:18">
       <x:c r="A2" s="0">
         <x:v>3</x:v>
       </x:c>
@@ -1027,7 +1056,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>17</x:v>
@@ -1036,40 +1065,46 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="J2" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K2" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="J2" s="0" t="s">
+      <x:c r="L2" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="K2" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="L2" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P2" s="2" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:16">
+      <x:c r="P2" s="0">
+        <x:v>62936</x:v>
+      </x:c>
+      <x:c r="Q2" s="0">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="R2" s="2" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:18">
       <x:c r="A3" s="0">
         <x:v>3</x:v>
       </x:c>
@@ -1077,7 +1112,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>17</x:v>
@@ -1086,40 +1121,46 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J3" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="M3" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N3" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P3" s="0">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="Q3" s="0">
+        <x:v>62936</x:v>
+      </x:c>
+      <x:c r="R3" s="2" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I3" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="J3" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="K3" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="L3" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="M3" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="N3" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="O3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P3" s="2" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:16">
+    </x:row>
+    <x:row r="4" spans="1:18">
       <x:c r="A4" s="0">
         <x:v>3</x:v>
       </x:c>
@@ -1127,7 +1168,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1136,40 +1177,46 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P4" s="2" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:16">
+      <x:c r="P4" s="0">
+        <x:v>62936</x:v>
+      </x:c>
+      <x:c r="Q4" s="0">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="R4" s="2" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:18">
       <x:c r="A5" s="0">
         <x:v>3</x:v>
       </x:c>
@@ -1177,7 +1224,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1186,40 +1233,46 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O5" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="P5" s="2" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:16">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="P5" s="0">
+        <x:v>62936</x:v>
+      </x:c>
+      <x:c r="Q5" s="0">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="R5" s="2" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:18">
       <x:c r="A6" s="0">
         <x:v>3</x:v>
       </x:c>
@@ -1227,7 +1280,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1236,40 +1289,46 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P6" s="2" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:16">
+      <x:c r="P6" s="0">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="Q6" s="0">
+        <x:v>62936</x:v>
+      </x:c>
+      <x:c r="R6" s="2" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:18">
       <x:c r="A7" s="0">
         <x:v>3</x:v>
       </x:c>
@@ -1277,7 +1336,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>17</x:v>
@@ -1286,40 +1345,46 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M7" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N7" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O7" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="P7" s="2" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:16">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="P7" s="0">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="Q7" s="0">
+        <x:v>62936</x:v>
+      </x:c>
+      <x:c r="R7" s="2" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:18">
       <x:c r="A8" s="0">
         <x:v>3</x:v>
       </x:c>
@@ -1327,7 +1392,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>17</x:v>
@@ -1336,40 +1401,46 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P8" s="2" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:16">
+      <x:c r="P8" s="0">
+        <x:v>62936</x:v>
+      </x:c>
+      <x:c r="Q8" s="0">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="R8" s="2" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:18">
       <x:c r="A9" s="0">
         <x:v>3</x:v>
       </x:c>
@@ -1377,7 +1448,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>17</x:v>
@@ -1386,40 +1457,46 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N9" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P9" s="3" t="s">
-        <x:v>57</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:16">
+      <x:c r="P9" s="0">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="Q9" s="0">
+        <x:v>62936</x:v>
+      </x:c>
+      <x:c r="R9" s="3" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:18">
       <x:c r="A10" s="0">
         <x:v>3</x:v>
       </x:c>
@@ -1427,7 +1504,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
         <x:v>17</x:v>
@@ -1436,40 +1513,46 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N10" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P10" s="3" t="s">
-        <x:v>57</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:16">
+      <x:c r="P10" s="0">
+        <x:v>62936</x:v>
+      </x:c>
+      <x:c r="Q10" s="0">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="R10" s="3" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:18">
       <x:c r="A11" s="0">
         <x:v>3</x:v>
       </x:c>
@@ -1477,7 +1560,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
         <x:v>17</x:v>
@@ -1486,40 +1569,46 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J11" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="M11" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N11" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O11" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P11" s="3" t="s">
-        <x:v>57</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:16">
+      <x:c r="P11" s="0">
+        <x:v>62936</x:v>
+      </x:c>
+      <x:c r="Q11" s="0">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="R11" s="3" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:18">
       <x:c r="A12" s="0">
         <x:v>3</x:v>
       </x:c>
@@ -1527,7 +1616,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
         <x:v>17</x:v>
@@ -1536,40 +1625,46 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L12" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M12" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N12" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O12" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P12" s="3" t="s">
-        <x:v>57</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:16">
+      <x:c r="P12" s="0">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="Q12" s="0">
+        <x:v>62936</x:v>
+      </x:c>
+      <x:c r="R12" s="3" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:18">
       <x:c r="A13" s="0">
         <x:v>6</x:v>
       </x:c>
@@ -1577,7 +1672,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
         <x:v>17</x:v>
@@ -1586,40 +1681,46 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="J13" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K13" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="J13" s="0" t="s">
+      <x:c r="L13" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="K13" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="L13" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
       <x:c r="M13" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N13" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O13" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P13" s="2" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:16">
+      <x:c r="P13" s="0">
+        <x:v>62944</x:v>
+      </x:c>
+      <x:c r="Q13" s="0">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="R13" s="2" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:18">
       <x:c r="A14" s="0">
         <x:v>6</x:v>
       </x:c>
@@ -1627,7 +1728,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
         <x:v>17</x:v>
@@ -1636,40 +1737,46 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I14" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J14" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="K14" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="L14" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="M14" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N14" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P14" s="0">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="Q14" s="0">
+        <x:v>62944</x:v>
+      </x:c>
+      <x:c r="R14" s="2" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="H14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I14" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="J14" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="K14" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="L14" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="M14" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="N14" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="O14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P14" s="2" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:16">
+    </x:row>
+    <x:row r="15" spans="1:18">
       <x:c r="A15" s="0">
         <x:v>6</x:v>
       </x:c>
@@ -1677,7 +1784,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
         <x:v>17</x:v>
@@ -1686,40 +1793,46 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J15" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L15" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M15" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N15" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O15" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P15" s="2" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:16">
+      <x:c r="P15" s="0">
+        <x:v>62944</x:v>
+      </x:c>
+      <x:c r="Q15" s="0">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="R15" s="2" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:18">
       <x:c r="A16" s="0">
         <x:v>6</x:v>
       </x:c>
@@ -1727,7 +1840,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
         <x:v>17</x:v>
@@ -1736,40 +1849,46 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J16" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="L16" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M16" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N16" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O16" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="P16" s="2" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:16">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="P16" s="0">
+        <x:v>62944</x:v>
+      </x:c>
+      <x:c r="Q16" s="0">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="R16" s="2" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:18">
       <x:c r="A17" s="0">
         <x:v>6</x:v>
       </x:c>
@@ -1777,7 +1896,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
         <x:v>17</x:v>
@@ -1786,40 +1905,46 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J17" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L17" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M17" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N17" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O17" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P17" s="2" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:16">
+      <x:c r="P17" s="0">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="Q17" s="0">
+        <x:v>62944</x:v>
+      </x:c>
+      <x:c r="R17" s="2" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:18">
       <x:c r="A18" s="0">
         <x:v>6</x:v>
       </x:c>
@@ -1827,7 +1952,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
         <x:v>17</x:v>
@@ -1836,40 +1961,46 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J18" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="L18" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M18" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N18" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O18" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="P18" s="2" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:16">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="P18" s="0">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="Q18" s="0">
+        <x:v>62944</x:v>
+      </x:c>
+      <x:c r="R18" s="2" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:18">
       <x:c r="A19" s="0">
         <x:v>6</x:v>
       </x:c>
@@ -1877,7 +2008,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
         <x:v>17</x:v>
@@ -1886,40 +2017,46 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I19" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J19" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L19" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M19" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N19" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O19" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P19" s="2" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:16">
+      <x:c r="P19" s="0">
+        <x:v>62944</x:v>
+      </x:c>
+      <x:c r="Q19" s="0">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="R19" s="2" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:18">
       <x:c r="A20" s="0">
         <x:v>6</x:v>
       </x:c>
@@ -1927,7 +2064,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
         <x:v>17</x:v>
@@ -1936,40 +2073,46 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I20" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="L20" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="M20" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N20" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O20" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P20" s="3" t="s">
-        <x:v>57</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:16">
+      <x:c r="P20" s="0">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="Q20" s="0">
+        <x:v>62944</x:v>
+      </x:c>
+      <x:c r="R20" s="3" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:18">
       <x:c r="A21" s="0">
         <x:v>6</x:v>
       </x:c>
@@ -1977,7 +2120,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
         <x:v>17</x:v>
@@ -1986,40 +2129,46 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I21" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J21" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L21" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M21" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N21" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O21" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P21" s="3" t="s">
-        <x:v>57</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:16">
+      <x:c r="P21" s="0">
+        <x:v>62944</x:v>
+      </x:c>
+      <x:c r="Q21" s="0">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="R21" s="3" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:18">
       <x:c r="A22" s="0">
         <x:v>6</x:v>
       </x:c>
@@ -2027,7 +2176,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
         <x:v>17</x:v>
@@ -2036,40 +2185,46 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I22" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J22" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="L22" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="M22" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N22" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O22" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P22" s="3" t="s">
-        <x:v>57</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:16">
+      <x:c r="P22" s="0">
+        <x:v>62944</x:v>
+      </x:c>
+      <x:c r="Q22" s="0">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="R22" s="3" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:18">
       <x:c r="A23" s="0">
         <x:v>6</x:v>
       </x:c>
@@ -2077,7 +2232,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
         <x:v>17</x:v>
@@ -2086,37 +2241,43 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I23" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L23" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M23" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N23" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O23" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P23" s="3" t="s">
-        <x:v>57</x:v>
+      <x:c r="P23" s="0">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="Q23" s="0">
+        <x:v>62944</x:v>
+      </x:c>
+      <x:c r="R23" s="3" t="s">
+        <x:v>63</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Hand_edited_log/1/student/AnhDThe187386/TC6/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/AnhDThe187386/TC6/GradeDetail.xlsx
@@ -1095,10 +1095,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>62936</x:v>
+        <x:v>51760</x:v>
       </x:c>
       <x:c r="Q2" s="0">
-        <x:v>4003</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>48</x:v>
@@ -1151,10 +1151,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P3" s="0">
-        <x:v>4003</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>62936</x:v>
+        <x:v>51760</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>48</x:v>
@@ -1207,10 +1207,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>62936</x:v>
+        <x:v>51760</x:v>
       </x:c>
       <x:c r="Q4" s="0">
-        <x:v>4003</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R4" s="2" t="s">
         <x:v>48</x:v>
@@ -1263,10 +1263,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>62936</x:v>
+        <x:v>51760</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>4003</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R5" s="2" t="s">
         <x:v>48</x:v>
@@ -1319,10 +1319,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>4003</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>62936</x:v>
+        <x:v>51760</x:v>
       </x:c>
       <x:c r="R6" s="2" t="s">
         <x:v>48</x:v>
@@ -1375,10 +1375,10 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="P7" s="0">
-        <x:v>4003</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>62936</x:v>
+        <x:v>51760</x:v>
       </x:c>
       <x:c r="R7" s="2" t="s">
         <x:v>48</x:v>
@@ -1431,10 +1431,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>62936</x:v>
+        <x:v>51760</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>4003</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R8" s="2" t="s">
         <x:v>48</x:v>
@@ -1487,10 +1487,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>4003</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>62936</x:v>
+        <x:v>51760</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>63</x:v>
@@ -1543,10 +1543,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>62936</x:v>
+        <x:v>51760</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>4003</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R10" s="3" t="s">
         <x:v>63</x:v>
@@ -1599,10 +1599,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>62936</x:v>
+        <x:v>51760</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>4003</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R11" s="3" t="s">
         <x:v>63</x:v>
@@ -1655,10 +1655,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P12" s="0">
-        <x:v>4003</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q12" s="0">
-        <x:v>62936</x:v>
+        <x:v>51760</x:v>
       </x:c>
       <x:c r="R12" s="3" t="s">
         <x:v>63</x:v>
@@ -1711,10 +1711,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P13" s="0">
-        <x:v>62944</x:v>
+        <x:v>51768</x:v>
       </x:c>
       <x:c r="Q13" s="0">
-        <x:v>4003</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R13" s="2" t="s">
         <x:v>48</x:v>
@@ -1767,10 +1767,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P14" s="0">
-        <x:v>4003</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q14" s="0">
-        <x:v>62944</x:v>
+        <x:v>51768</x:v>
       </x:c>
       <x:c r="R14" s="2" t="s">
         <x:v>48</x:v>
@@ -1823,10 +1823,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P15" s="0">
-        <x:v>62944</x:v>
+        <x:v>51768</x:v>
       </x:c>
       <x:c r="Q15" s="0">
-        <x:v>4003</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R15" s="2" t="s">
         <x:v>48</x:v>
@@ -1879,10 +1879,10 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="P16" s="0">
-        <x:v>62944</x:v>
+        <x:v>51768</x:v>
       </x:c>
       <x:c r="Q16" s="0">
-        <x:v>4003</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R16" s="2" t="s">
         <x:v>48</x:v>
@@ -1935,10 +1935,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P17" s="0">
-        <x:v>4003</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q17" s="0">
-        <x:v>62944</x:v>
+        <x:v>51768</x:v>
       </x:c>
       <x:c r="R17" s="2" t="s">
         <x:v>48</x:v>
@@ -1991,10 +1991,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="P18" s="0">
-        <x:v>4003</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q18" s="0">
-        <x:v>62944</x:v>
+        <x:v>51768</x:v>
       </x:c>
       <x:c r="R18" s="2" t="s">
         <x:v>48</x:v>
@@ -2047,10 +2047,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P19" s="0">
-        <x:v>62944</x:v>
+        <x:v>51768</x:v>
       </x:c>
       <x:c r="Q19" s="0">
-        <x:v>4003</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R19" s="2" t="s">
         <x:v>48</x:v>
@@ -2103,10 +2103,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P20" s="0">
-        <x:v>4003</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q20" s="0">
-        <x:v>62944</x:v>
+        <x:v>51768</x:v>
       </x:c>
       <x:c r="R20" s="3" t="s">
         <x:v>63</x:v>
@@ -2159,10 +2159,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P21" s="0">
-        <x:v>62944</x:v>
+        <x:v>51768</x:v>
       </x:c>
       <x:c r="Q21" s="0">
-        <x:v>4003</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R21" s="3" t="s">
         <x:v>63</x:v>
@@ -2215,10 +2215,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P22" s="0">
-        <x:v>62944</x:v>
+        <x:v>51768</x:v>
       </x:c>
       <x:c r="Q22" s="0">
-        <x:v>4003</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R22" s="3" t="s">
         <x:v>63</x:v>
@@ -2271,10 +2271,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P23" s="0">
-        <x:v>4003</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q23" s="0">
-        <x:v>62944</x:v>
+        <x:v>51768</x:v>
       </x:c>
       <x:c r="R23" s="3" t="s">
         <x:v>63</x:v>
